--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="560" documentId="8_{063A5964-0365-43B4-B470-8DEE6E7CD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5715A896-7FCC-47D7-86D3-C77A9A93E501}"/>
+  <xr:revisionPtr revIDLastSave="2695" documentId="8_{063A5964-0365-43B4-B470-8DEE6E7CD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E932B2C8-F2C1-439E-B035-1804ABD524F0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
+    <workbookView xWindow="6345" yWindow="1125" windowWidth="21570" windowHeight="11295" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.2</v>
+        <v>1.9998199999999999</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>706.5</v>
+        <v>176.625</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="B8">
         <f>k_lid*area_lid*(set_temp-dt_cool)/thickness_lid</f>
-        <v>1192.2187499999998</v>
+        <v>29.808151483633523</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15302" documentId="8_{063A5964-0365-43B4-B470-8DEE6E7CD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6723FF3C-0949-4C90-A1E7-A777146C39E9}"/>
+  <xr:revisionPtr revIDLastSave="47145" documentId="8_{063A5964-0365-43B4-B470-8DEE6E7CD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7A7F9FA-A97B-4FCF-932B-BDF22FE3DEC0}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
@@ -503,7 +503,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
       <c r="B5">
-        <v>706.5</v>
+        <v>176.625</v>
       </c>
       <c r="C5" t="s">
         <v>3</v>
@@ -548,7 +548,7 @@
       </c>
       <c r="B8">
         <f>k_lid*area_lid*(set_temp-dt_cool)/thickness_lid</f>
-        <v>662.34374999999989</v>
+        <v>298.05468749999994</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -570,7 +570,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>1.1775105975</v>
+        <v>0.58875</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -582,7 +582,7 @@
       </c>
       <c r="B12">
         <f>fluid_mass*c_water*dt_cool</f>
-        <v>73900.5650991</v>
+        <v>36949.949999999997</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="630" documentId="8_{063A5964-0365-43B4-B470-8DEE6E7CD90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F9C374-E4CF-4E55-B275-75305578603D}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D98FF8A6-562E-4EC3-9CFA-3EE4EAF7C929}"/>
   <bookViews>
-    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
+    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,7 +566,7 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.58874952899999999</v>
+        <v>0.5</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -578,7 +578,7 @@
       </c>
       <c r="B12">
         <f>fluid_mass*c_water*dt_cool</f>
-        <v>36949.920440039998</v>
+        <v>31380</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D98FF8A6-562E-4EC3-9CFA-3EE4EAF7C929}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3708CD7-1F58-4C25-B1AB-9A055EDA904A}"/>
   <bookViews>
-    <workbookView xWindow="6795" yWindow="30" windowWidth="21570" windowHeight="11295" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
+    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -153,6 +153,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -532,7 +536,7 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -544,7 +548,7 @@
       </c>
       <c r="B8">
         <f>k_lid*area_lid*(set_temp-dt_cool)/thickness_lid</f>
-        <v>1192.2187499999998</v>
+        <v>1033.2562499999999</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -578,7 +582,7 @@
       </c>
       <c r="B12">
         <f>fluid_mass*c_water*dt_cool</f>
-        <v>31380</v>
+        <v>52300</v>
       </c>
       <c r="C12" t="s">
         <v>10</v>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/lcalimlim3_gatech_edu/Documents/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3708CD7-1F58-4C25-B1AB-9A055EDA904A}"/>
+  <xr:revisionPtr revIDLastSave="14042" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9A31F3-3824-4018-A434-3AF037F757AE}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="420" windowWidth="21570" windowHeight="11295" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
+    <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14042" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9A31F3-3824-4018-A434-3AF037F757AE}"/>
+  <xr:revisionPtr revIDLastSave="19434" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECAFF79-9C22-4BA3-8D6E-4C7E70B24348}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19434" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EECAFF79-9C22-4BA3-8D6E-4C7E70B24348}"/>
+  <xr:revisionPtr revIDLastSave="19640" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D2C6818-4A41-4402-9827-28774D888D2A}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <definedName name="set_temp">Sheet1!$B$6</definedName>
     <definedName name="thickness_lid">Sheet1!$B$4</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19640" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D2C6818-4A41-4402-9827-28774D888D2A}"/>
+  <xr:revisionPtr revIDLastSave="21901" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC08F02-5755-46AD-8EE3-BD7682000A01}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>

--- a/Q_Cool/Q_Cool.xlsx
+++ b/Q_Cool/Q_Cool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07531a99d7244c5b/Documents/GitHub/ASE6002PEK/Q_Cool/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21901" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9FC08F02-5755-46AD-8EE3-BD7682000A01}"/>
+  <xr:revisionPtr revIDLastSave="28901" documentId="114_{FF5EDC6A-1FA3-4945-9C9C-BB383A9F0039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3957CAE8-A782-4334-9A62-17BEF7EAA3EC}"/>
   <bookViews>
     <workbookView xWindow="9105" yWindow="5325" windowWidth="38700" windowHeight="15345" xr2:uid="{88502E7A-6C66-4183-A361-D0DC5516A7E2}"/>
   </bookViews>
